--- a/backtest_runs/20260410_193731/by_symbol/REDCO/REDCO.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/REDCO/REDCO.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-8917.380000000003</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>95499.63999999998</v>
@@ -955,7 +955,7 @@
         <v>-7250.579999999994</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>99624.97</v>
@@ -1185,7 +1185,7 @@
         <v>-7667.28</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>108834.04</v>
@@ -1323,7 +1323,7 @@
         <v>-11000.88</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>118334.8</v>
@@ -1461,7 +1461,7 @@
         <v>-9250.739999999996</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>116376.31</v>
@@ -1507,7 +1507,7 @@
         <v>-1958.49000000001</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>114417.82</v>
@@ -1645,7 +1645,7 @@
         <v>-1166.760000000005</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>121335.04</v>
